--- a/collectibles_market_dashboard.xlsx
+++ b/collectibles_market_dashboard.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Downloads\Collectibles_Market_Research\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC6AB75-AEC9-4BD7-896E-311C1AE6E429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8284E6D7-086C-43B0-B3A6-EF8856B09505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,15 +21,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
-  <si>
-    <t>Collectibles Market Research — Luxury Watch Index vs Traditional Assets</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="57">
+  <si>
+    <t>Collectibles Market Research — Price Index vs Traditional Assets (2015–2025)</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>Watch Index</t>
+    <t>Luxury Watches</t>
+  </si>
+  <si>
+    <t>Sneakers</t>
+  </si>
+  <si>
+    <t>Sports Cards</t>
   </si>
   <si>
     <t>S&amp;P 500</t>
@@ -38,12 +44,15 @@
     <t>Gold</t>
   </si>
   <si>
-    <t>Watch vs S&amp;P (pp)</t>
+    <t>Best Collectible</t>
   </si>
   <si>
     <t>2015-01-01</t>
   </si>
   <si>
+    <t>Watches</t>
+  </si>
+  <si>
     <t>2016-01-01</t>
   </si>
   <si>
@@ -56,6 +65,9 @@
     <t>2019-01-01</t>
   </si>
   <si>
+    <t>Cards</t>
+  </si>
+  <si>
     <t>2020-01-01</t>
   </si>
   <si>
@@ -74,7 +86,7 @@
     <t>2025-01-01</t>
   </si>
   <si>
-    <t>Summary Statistics — 2015 to 2025</t>
+    <t>Summary Statistics — All Markets (2015–2025)</t>
   </si>
   <si>
     <t>Metric</t>
@@ -86,6 +98,12 @@
     <t>116.4%</t>
   </si>
   <si>
+    <t>50.8%</t>
+  </si>
+  <si>
+    <t>515.8%</t>
+  </si>
+  <si>
     <t>130.4%</t>
   </si>
   <si>
@@ -98,6 +116,12 @@
     <t>8.02%</t>
   </si>
   <si>
+    <t>4.19%</t>
+  </si>
+  <si>
+    <t>19.93%</t>
+  </si>
+  <si>
     <t>8.71%</t>
   </si>
   <si>
@@ -110,6 +134,12 @@
     <t>18.72%</t>
   </si>
   <si>
+    <t>28.12%</t>
+  </si>
+  <si>
+    <t>88.13%</t>
+  </si>
+  <si>
     <t>16.77%</t>
   </si>
   <si>
@@ -122,38 +152,53 @@
     <t>-32.11%</t>
   </si>
   <si>
+    <t>-57.78%</t>
+  </si>
+  <si>
+    <t>-58.21%</t>
+  </si>
+  <si>
     <t>-20.27%</t>
   </si>
   <si>
     <t>-9.35%</t>
   </si>
   <si>
+    <t>Peak Year</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
     <t>Peak Value (Indexed)</t>
   </si>
   <si>
     <t>318.7</t>
   </si>
   <si>
+    <t>357.1</t>
+  </si>
+  <si>
+    <t>1473.7</t>
+  </si>
+  <si>
     <t>233.0</t>
   </si>
   <si>
     <t>174.1</t>
-  </si>
-  <si>
-    <t>Peak Year</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>2024</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,7 +208,7 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
@@ -171,18 +216,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFE74C3C"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF2ECC71"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -221,16 +254,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -266,6 +296,21 @@
   <c:style val="10"/>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="it-IT"/>
+              <a:t>Collectibles vs Traditional Assets (Base = 100)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -283,7 +328,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Watch Index</c:v>
+                  <c:v>Luxury Watches</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -385,7 +430,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CA7C-4B6D-BBAE-E226DF2745B6}"/>
+              <c16:uniqueId val="{00000000-F3F2-4E30-AF68-5754F97C8D6D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -395,6 +440,236 @@
           <c:tx>
             <c:strRef>
               <c:f>'Performance Dashboard'!$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sneakers</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="6C63FF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Performance Dashboard'!$A$3:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2015-01-01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2016-01-01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2017-01-01</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2018-01-01</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2019-01-01</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2020-01-01</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2021-01-01</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2022-01-01</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2023-01-01</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2024-01-01</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2025-01-01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Performance Dashboard'!$C$3:$C$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>131.69999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>166.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>195.2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>201.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>214.3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>341.3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>357.1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>171.4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>150.80000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-F3F2-4E30-AF68-5754F97C8D6D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Performance Dashboard'!$D$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sports Cards</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="2ECC71"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Performance Dashboard'!$A$3:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2015-01-01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2016-01-01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2017-01-01</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2018-01-01</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2019-01-01</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2020-01-01</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2021-01-01</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2022-01-01</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2023-01-01</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2024-01-01</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2025-01-01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Performance Dashboard'!$D$3:$D$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>121.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>147.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>189.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>247.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>394.7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1473.7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1105.3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>736.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>657.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>615.79999999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-F3F2-4E30-AF68-5754F97C8D6D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Performance Dashboard'!$E$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -457,7 +732,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Performance Dashboard'!$C$3:$C$13</c:f>
+              <c:f>'Performance Dashboard'!$E$3:$E$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -500,16 +775,16 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-CA7C-4B6D-BBAE-E226DF2745B6}"/>
+              <c16:uniqueId val="{00000003-F3F2-4E30-AF68-5754F97C8D6D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:idx val="4"/>
+          <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Performance Dashboard'!$D$2</c:f>
+              <c:f>'Performance Dashboard'!$F$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -572,7 +847,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Performance Dashboard'!$D$3:$D$13</c:f>
+              <c:f>'Performance Dashboard'!$F$3:$F$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -615,7 +890,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-CA7C-4B6D-BBAE-E226DF2745B6}"/>
+              <c16:uniqueId val="{00000004-F3F2-4E30-AF68-5754F97C8D6D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -691,12 +966,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7200000" cy="5040000"/>
+    <xdr:ext cx="7920000" cy="5040000"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -1008,22 +1283,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="22" customWidth="1"/>
+    <col min="1" max="7" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1039,10 +1316,16 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>100</v>
@@ -1053,183 +1336,249 @@
       <c r="D3">
         <v>100</v>
       </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>100</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2">
         <v>106.7</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
+        <v>131.69999999999999</v>
+      </c>
+      <c r="D4" s="2">
+        <v>121.1</v>
+      </c>
+      <c r="E4" s="2">
         <v>97.8</v>
       </c>
-      <c r="D4" s="3">
+      <c r="F4" s="2">
         <v>90.6</v>
       </c>
-      <c r="E4" s="4">
-        <v>8.9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>117</v>
       </c>
       <c r="C5">
+        <v>166.7</v>
+      </c>
+      <c r="D5">
+        <v>147.4</v>
+      </c>
+      <c r="E5">
         <v>109.7</v>
       </c>
-      <c r="D5">
+      <c r="F5">
         <v>97.8</v>
       </c>
-      <c r="E5" s="5">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="3">
+      <c r="G5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2">
         <v>133.9</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
+        <v>195.2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>189.5</v>
+      </c>
+      <c r="E6" s="2">
         <v>131</v>
       </c>
-      <c r="D6" s="3">
+      <c r="F6" s="2">
         <v>110.8</v>
       </c>
-      <c r="E6" s="4">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G6" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <v>150.6</v>
       </c>
       <c r="C7">
+        <v>201.6</v>
+      </c>
+      <c r="D7">
+        <v>247.4</v>
+      </c>
+      <c r="E7">
         <v>122</v>
       </c>
-      <c r="D7">
+      <c r="F7">
         <v>108</v>
       </c>
-      <c r="E7" s="5">
-        <v>28.6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="3">
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="2">
         <v>168.1</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
+        <v>214.3</v>
+      </c>
+      <c r="D8" s="2">
+        <v>394.7</v>
+      </c>
+      <c r="E8" s="2">
         <v>158.30000000000001</v>
       </c>
-      <c r="D8" s="3">
+      <c r="F8" s="2">
         <v>128.5</v>
       </c>
-      <c r="E8" s="4">
-        <v>9.8000000000000007</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>222.2</v>
       </c>
       <c r="C9">
+        <v>341.3</v>
+      </c>
+      <c r="D9">
+        <v>1473.7</v>
+      </c>
+      <c r="E9">
         <v>179.8</v>
       </c>
-      <c r="D9">
+      <c r="F9">
         <v>164</v>
       </c>
-      <c r="E9" s="5">
-        <v>42.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="3">
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2">
         <v>318.7</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
+        <v>357.1</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1105.3</v>
+      </c>
+      <c r="E10" s="2">
         <v>233</v>
       </c>
-      <c r="D10" s="3">
+      <c r="F10" s="2">
         <v>151.69999999999999</v>
       </c>
-      <c r="E10" s="4">
-        <v>85.7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G10" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B11">
         <v>263.2</v>
       </c>
       <c r="C11">
+        <v>219</v>
+      </c>
+      <c r="D11">
+        <v>736.8</v>
+      </c>
+      <c r="E11">
         <v>185.8</v>
       </c>
-      <c r="D11">
+      <c r="F11">
         <v>155.1</v>
       </c>
-      <c r="E11" s="5">
-        <v>77.400000000000006</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="3">
+      <c r="G11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="2">
         <v>232.5</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
+        <v>171.4</v>
+      </c>
+      <c r="D12" s="2">
+        <v>657.9</v>
+      </c>
+      <c r="E12" s="2">
         <v>230.4</v>
       </c>
-      <c r="D12" s="3">
+      <c r="F12" s="2">
         <v>174.1</v>
       </c>
-      <c r="E12" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G12" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>216.4</v>
       </c>
       <c r="C13">
+        <v>150.80000000000001</v>
+      </c>
+      <c r="D13">
+        <v>615.79999999999995</v>
+      </c>
+      <c r="E13">
         <v>230.4</v>
       </c>
-      <c r="D13">
+      <c r="F13">
         <v>174.1</v>
       </c>
-      <c r="E13" s="2">
-        <v>-14.1</v>
+      <c r="G13" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -1238,26 +1587,28 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="22" customWidth="1"/>
+    <col min="1" max="6" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
@@ -1265,94 +1616,136 @@
       <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D3" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="F3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="7" t="s">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="D4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="E4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="F4" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D5" s="4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="E5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="F5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="8" t="s">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>41</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
